--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03(Linh Kiện Thu Lại Gia Công)_240626.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Xuất kho/Tháng 06/XKSX_LinhKienGiaCongVNSH03(Linh Kiện Thu Lại Gia Công)_240626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8ADFDF9-4644-48AD-AF3A-6810612DE2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BDE138-8AE5-40AF-B4D2-179C54DFB29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">XuatKho_SX!$A$9:$F$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">XuatKho_SX!$A$1:$J$51</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="60">
   <si>
     <t>STT</t>
   </si>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>Linh Kiện Thừa Sau Khi Sủa BOM</t>
+  </si>
+  <si>
+    <t>EMK316BBJ476ML-T</t>
+  </si>
+  <si>
+    <t>DLM0NSN900HY2D</t>
   </si>
 </sst>
 </file>
@@ -332,7 +338,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -439,43 +445,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -483,7 +452,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -616,13 +585,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -632,7 +595,47 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -662,13 +665,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>488016</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>307037</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>3941</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1047,7 +1050,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L64"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.140625" style="1" customWidth="1"/>
@@ -1164,7 +1167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20">
         <v>1</v>
       </c>
@@ -1197,8 +1200,8 @@
       <c r="D11" s="23">
         <v>500</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
     </row>
     <row r="12" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="20">
@@ -1213,8 +1216,8 @@
       <c r="D12" s="23">
         <v>600</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
     </row>
     <row r="13" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="20">
@@ -1229,8 +1232,8 @@
       <c r="D13" s="23">
         <v>340</v>
       </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="20">
@@ -1245,8 +1248,8 @@
       <c r="D14" s="23">
         <v>100</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
     </row>
     <row r="15" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="20">
@@ -1261,8 +1264,8 @@
       <c r="D15" s="23">
         <v>500</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="20">
@@ -1277,8 +1280,8 @@
       <c r="D16" s="23">
         <v>5300</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
     </row>
     <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="20">
@@ -1293,8 +1296,8 @@
       <c r="D17" s="23">
         <v>1000</v>
       </c>
-      <c r="E17" s="47"/>
-      <c r="F17" s="47"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
     </row>
     <row r="18" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="20">
@@ -1309,8 +1312,8 @@
       <c r="D18" s="23">
         <v>1000</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
     </row>
     <row r="19" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="20">
@@ -1325,8 +1328,8 @@
       <c r="D19" s="23">
         <v>1000</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
     </row>
     <row r="20" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="20">
@@ -1341,8 +1344,8 @@
       <c r="D20" s="23">
         <v>500</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
     </row>
     <row r="21" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="20">
@@ -1357,8 +1360,8 @@
       <c r="D21" s="23">
         <v>500</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
     </row>
     <row r="22" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="20">
@@ -1373,8 +1376,8 @@
       <c r="D22" s="23">
         <v>500</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
     </row>
     <row r="23" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="20">
@@ -1389,8 +1392,8 @@
       <c r="D23" s="23">
         <v>500</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
     </row>
     <row r="24" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="20">
@@ -1405,8 +1408,8 @@
       <c r="D24" s="23">
         <v>120</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
     </row>
     <row r="25" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="20">
@@ -1421,8 +1424,8 @@
       <c r="D25" s="23">
         <v>1400</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="46"/>
     </row>
     <row r="26" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="20">
@@ -1437,8 +1440,8 @@
       <c r="D26" s="23">
         <v>500</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
     </row>
     <row r="27" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="20">
@@ -1453,8 +1456,8 @@
       <c r="D27" s="23">
         <v>500</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
     </row>
     <row r="28" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="20">
@@ -1469,8 +1472,8 @@
       <c r="D28" s="23">
         <v>500</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
     </row>
     <row r="29" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="20">
@@ -1485,8 +1488,8 @@
       <c r="D29" s="23">
         <v>3500</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
     </row>
     <row r="30" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="20">
@@ -1501,8 +1504,8 @@
       <c r="D30" s="23">
         <v>500</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
     </row>
     <row r="31" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="20">
@@ -1517,8 +1520,8 @@
       <c r="D31" s="23">
         <v>500</v>
       </c>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
     </row>
     <row r="32" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="20">
@@ -1533,8 +1536,8 @@
       <c r="D32" s="23">
         <v>500</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="47"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
     </row>
     <row r="33" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="20">
@@ -1549,8 +1552,8 @@
       <c r="D33" s="23">
         <v>500</v>
       </c>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
     </row>
     <row r="34" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="20">
@@ -1565,8 +1568,8 @@
       <c r="D34" s="23">
         <v>500</v>
       </c>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="46"/>
     </row>
     <row r="35" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="20">
@@ -1581,8 +1584,8 @@
       <c r="D35" s="23">
         <v>500</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="47"/>
+      <c r="E35" s="46"/>
+      <c r="F35" s="46"/>
     </row>
     <row r="36" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="20">
@@ -1597,8 +1600,8 @@
       <c r="D36" s="23">
         <v>500</v>
       </c>
-      <c r="E36" s="47"/>
-      <c r="F36" s="47"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
     </row>
     <row r="37" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="20">
@@ -1613,8 +1616,8 @@
       <c r="D37" s="23">
         <v>1000</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
     </row>
     <row r="38" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="20">
@@ -1629,8 +1632,8 @@
       <c r="D38" s="23">
         <v>5500</v>
       </c>
-      <c r="E38" s="47"/>
-      <c r="F38" s="47"/>
+      <c r="E38" s="46"/>
+      <c r="F38" s="46"/>
     </row>
     <row r="39" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="20">
@@ -1645,78 +1648,94 @@
       <c r="D39" s="23">
         <v>500</v>
       </c>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
     </row>
     <row r="40" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="8"/>
+      <c r="A40" s="20">
+        <v>31</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="23">
+        <v>500</v>
+      </c>
+      <c r="E40" s="46"/>
+      <c r="F40" s="46"/>
     </row>
     <row r="41" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="8"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
+      <c r="A41" s="20">
+        <v>32</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="23">
+        <v>500</v>
+      </c>
+      <c r="E41" s="46"/>
+      <c r="F41" s="46"/>
     </row>
     <row r="42" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="44" t="s">
+      <c r="A42" s="6"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="8"/>
+    </row>
+    <row r="43" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="8"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="44"/>
-      <c r="C42" s="44" t="s">
+      <c r="B44" s="44"/>
+      <c r="C44" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="D42" s="44"/>
-      <c r="E42" s="25" t="s">
+      <c r="D44" s="44"/>
+      <c r="E44" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="25" t="s">
+      <c r="F44" s="25" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="45" t="s">
+    <row r="45" spans="1:6" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45" t="s">
+      <c r="B45" s="45"/>
+      <c r="C45" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="45"/>
-      <c r="E43" s="28" t="s">
+      <c r="D45" s="45"/>
+      <c r="E45" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F43" s="28" t="s">
+      <c r="F45" s="28" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="26"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="26"/>
-    </row>
-    <row r="45" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="26"/>
     </row>
     <row r="46" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="26"/>
       <c r="B46" s="26"/>
       <c r="C46" s="26"/>
-      <c r="D46" s="24"/>
+      <c r="D46" s="26"/>
       <c r="E46" s="27"/>
       <c r="F46" s="26"/>
     </row>
@@ -1725,64 +1744,80 @@
       <c r="B47" s="26"/>
       <c r="C47" s="26"/>
       <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
+      <c r="E47" s="27"/>
       <c r="F47" s="26"/>
     </row>
     <row r="48" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="26"/>
       <c r="B48" s="26"/>
       <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
+      <c r="D48" s="24"/>
       <c r="E48" s="27"/>
       <c r="F48" s="26"/>
     </row>
-    <row r="49" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="44" t="s">
+    <row r="49" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+    </row>
+    <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="26"/>
+    </row>
+    <row r="51" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44" t="s">
+      <c r="B51" s="44"/>
+      <c r="C51" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="D49" s="44"/>
-      <c r="E49" s="25" t="s">
+      <c r="D51" s="44"/>
+      <c r="E51" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="F49" s="25" t="s">
+      <c r="F51" s="25" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-    </row>
     <row r="52" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+    </row>
     <row r="54" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-    </row>
+    <row r="55" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="F62" s="5"/>
+    <row r="57" spans="1:6" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="C57" s="11"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="11"/>
+      <c r="F57" s="11"/>
+    </row>
+    <row r="58" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="F64" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A9:F39" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="14">
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="E10:E39"/>
-    <mergeCell ref="F10:F39"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E10:E41"/>
+    <mergeCell ref="F10:F41"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:F3"/>
@@ -1790,7 +1825,17 @@
     <mergeCell ref="A1:B4"/>
   </mergeCells>
   <conditionalFormatting sqref="B10:B39">
-    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="99" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
